--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2590,34 +2590,34 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>12852000</v>
+        <v>9960000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>31043</v>
+        <v>24058</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>9896040</v>
+        <v>9960000</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>23903</v>
+        <v>24058</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-13</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2962,34 +2962,34 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>12481000</v>
+        <v>9673000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>30147</v>
+        <v>23365</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>9610370</v>
+        <v>9673000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>23213</v>
+        <v>23365</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3148,34 +3148,34 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>12360000</v>
+        <v>9579000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>29855</v>
+        <v>23138</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>9517200</v>
+        <v>9579000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>22988</v>
+        <v>23138</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-12-20</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3520,34 +3520,34 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>12122000</v>
+        <v>9395000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>29280</v>
+        <v>22693</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>9333940</v>
+        <v>9395000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>22546</v>
+        <v>22693</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-12-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5344,7 +5344,7 @@
           <t>C | 414呎 (1房)
 $1186万
 $28,643/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
           <t>A | 481呎 (2房)
 $1184万
 $24,605/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -5584,7 +5584,7 @@
           <t>B | 286呎 (1房)
 $708万
 $24,752/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -5618,12 +5618,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 414呎 (2房)
-$1285万
-$31,043/呎
-(在售)</t>
+$996万
+$24,058/呎
+(26年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
           <t>A | 465呎 (2房)
 $1247万
 $26,826/呎
-(23年-01月-12日)</t>
+(23年-01月-13日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -5646,7 +5646,7 @@
           <t>B | 286呎 (1房)
 $777万
 $27,164/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -5669,7 +5669,7 @@
           <t>A | 465呎 (2房)
 $1278万
 $27,482/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -5677,15 +5677,15 @@
           <t>B | 286呎 (1房)
 $769万
 $26,902/呎
-(23年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+(23年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 414呎 (2房)
-$1248万
-$30,147/呎
-(在售)</t>
+$967万
+$23,365/呎
+(26年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -5708,15 +5708,15 @@
           <t>B | 286呎 (1房)
 $679万
 $23,731/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 414呎 (2房)
-$1236万
-$29,855/呎
-(在售)</t>
+$958万
+$23,138/呎
+(26年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
           <t>B | 286呎 (1房)
 $763万
 $26,685/呎
-(22年-12月-19日)</t>
+(22年-12月-20日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -5762,7 +5762,7 @@
           <t>A | 465呎 (2房)
 $1241万
 $26,692/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -5770,15 +5770,15 @@
           <t>B | 286呎 (1房)
 $756万
 $26,427/呎
-(23年-01月-03日)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
+(23年-01月-04日)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 414呎 (2房)
-$1212万
-$29,280/呎
-(在售)</t>
+$940万
+$22,693/呎
+(26年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
           <t>A | 465呎 (2房)
 $1202万
 $25,841/呎
-(23年-01月-09日)</t>
+(23年-01月-10日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -5801,7 +5801,7 @@
           <t>B | 286呎 (1房)
 $782万
 $27,357/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -5824,7 +5824,7 @@
           <t>A | 465呎 (2房)
 $1177万
 $25,305/呎
-(23年-05月-02日)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -5832,7 +5832,7 @@
           <t>B | 286呎 (1房)
 $741万
 $25,916/呎
-(23年-01月-03日)</t>
+(23年-01月-04日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -5840,7 +5840,7 @@
           <t>C | 414呎 (2房)
 $1046万
 $25,271/呎
-(22年-12月-04日)</t>
+(22年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
           <t>A | 481呎 (2房)
 $1154万
 $24,002/呎
-(23年-05月-29日)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -5863,7 +5863,7 @@
           <t>B | 286呎 (1房)
 $734万
 $25,661/呎
-(22年-12月-19日)</t>
+(22年-12月-20日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -5871,7 +5871,7 @@
           <t>C | 414呎 (2房)
 $912万
 $22,039/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
           <t>A | 481呎 (2房)
 $1172万
 $24,360/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -5894,7 +5894,7 @@
           <t>B | 286呎 (1房)
 $720万
 $25,171/呎
-(22年-10月-02日)</t>
+(22年-10月-03日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -5902,7 +5902,7 @@
           <t>C | 414呎 (2房)
 $1016万
 $24,546/呎
-(23年-04月-12日)</t>
+(23年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
           <t>B | 286呎 (1房)
 $689万
 $24,077/呎
-(22年-10月-04日)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -5933,7 +5933,7 @@
           <t>C | 414呎 (2房)
 $997万
 $24,082/呎
-(22年-09月-26日)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
           <t>A | 465呎 (2房)
 $1073万
 $23,069/呎
-(23年-01月-31日)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -5956,7 +5956,7 @@
           <t>B | 286呎 (1房)
 $738万
 $25,808/呎
-(21年-10月-03日)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -5964,7 +5964,7 @@
           <t>C | 414呎 (2房)
 $852万
 $20,592/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
           <t>A | 465呎 (2房)
 $968万
 $20,826/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -5987,7 +5987,7 @@
           <t>B | 286呎 (1房)
 $723万
 $25,283/呎
-(21年-08月-23日)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -5995,7 +5995,7 @@
           <t>C | 414呎 (2房)
 $971万
 $23,447/呎
-(21年-08月-24日)</t>
+(21年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
           <t>B | 286呎 (1房)
 $597万
 $20,885/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -6026,7 +6026,7 @@
           <t>C | 377呎 (2房)
 $1078万
 $28,600/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -1846,34 +1846,34 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>13364000</v>
+        <v>10357000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>32280</v>
+        <v>25017</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>10290280</v>
+        <v>10357000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>24856</v>
+        <v>25017</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2404,34 +2404,34 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>12977000</v>
+        <v>10057000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>31345</v>
+        <v>24292</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>9992290</v>
+        <v>10057000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>24136</v>
+        <v>24292</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5494,12 +5494,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 414呎 (2房)
-$1336万
-$32,280/呎
-(在售)</t>
+$1036万
+$25,017/呎
+(26年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -5587,12 +5587,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 414呎 (2房)
-$1298万
-$31,345/呎
-(在售)</t>
+$1006万
+$24,292/呎
+(26年-07月-31日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -6026,7 +6026,7 @@
           <t>C | 377呎 (2房)
 $1078万
 $28,600/呎
-(26年-07月-09日)</t>
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -5716,7 +5716,7 @@
           <t>C | 414呎 (2房)
 $958万
 $23,138/呎
-(26年-07月-28日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -5592,7 +5592,7 @@
           <t>C | 414呎 (2房)
 $1006万
 $24,292/呎
-(26年-07月-31日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
           <t>C | 414呎 (2房)
 $996万
 $24,058/呎
-(26年-07月-30日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
           <t>C | 414呎 (2房)
 $967万
 $23,365/呎
-(26年-07月-29日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
           <t>C | 414呎 (2房)
 $940万
 $22,693/呎
-(26年-07月-27日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -5499,7 +5499,7 @@
           <t>C | 414呎 (2房)
 $1036万
 $25,017/呎
-(26年-08月-01日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 481呎 (2房)
 $1440万
 $29,946/呎
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
